--- a/docs/insumos/plantilla-banco-de-preguntas.xlsx
+++ b/docs/insumos/plantilla-banco-de-preguntas.xlsx
@@ -916,13 +916,13 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="C30:E30"/>
     <mergeCell ref="C14:E14"/>
     <mergeCell ref="C31:E31"/>
     <mergeCell ref="C8:E8"/>
     <mergeCell ref="C9:E9"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="C29:E29"/>
+    <mergeCell ref="C30:E30"/>
     <mergeCell ref="C7:E7"/>
     <mergeCell ref="C6:E6"/>
     <mergeCell ref="C10:E10"/>
@@ -937,7 +937,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I74"/>
+  <dimension ref="A1:K74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -949,6 +949,8 @@
     <col width="26" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="34" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -965,6 +967,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="10" t="inlineStr">
         <is>
@@ -1011,6 +1014,16 @@
           <t>Nota interna (opcional)</t>
         </is>
       </c>
+      <c r="J4" s="10" t="inlineStr">
+        <is>
+          <t>Fórmula de puntaje (solo V)</t>
+        </is>
+      </c>
+      <c r="K4" s="10" t="inlineStr">
+        <is>
+          <t>Usa los rangos de (solo V)</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="34" customHeight="1">
       <c r="A5" s="14" t="inlineStr">
@@ -1056,6 +1069,16 @@
       <c r="I5" s="14" t="inlineStr">
         <is>
           <t>Guía para el evaluador. El candidato nunca la ve.</t>
+        </is>
+      </c>
+      <c r="J5" s="14" t="inlineStr">
+        <is>
+          <t>Si el ítem V no se puntúa por tramos: la fórmula, en palabras.</t>
+        </is>
+      </c>
+      <c r="K5" s="14" t="inlineStr">
+        <is>
+          <t>Si el ítem V usa la tabla de otra pregunta: su código.</t>
         </is>
       </c>
     </row>
